--- a/reports/weekly_report_20260615.xlsx
+++ b/reports/weekly_report_20260615.xlsx
@@ -178,12 +178,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'状态分布'!$A$2:$A$3</f>
+              <f>'状态分布'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'状态分布'!$B$2:$B$3</f>
+              <f>'状态分布'!$B$2:$B$6</f>
             </numRef>
           </val>
         </ser>
@@ -519,7 +519,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="8">
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>36.36</v>
       </c>
     </row>
     <row r="9">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -675,11 +675,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -733,82 +733,450 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>REL-20260619_093038</t>
+          <t>E2E-4-1781842360</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>v2.0619.38</t>
+          <t>v4.0.0-OTHER</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>常规发布</t>
+          <t>紧急发布</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>回滚失败</t>
+          <t>回滚成功</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>WMS 库存管理模块优化</t>
+          <t>问题4测试-其他版本</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>developer01</t>
+          <t>e2e</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-19 09:30:38</t>
+          <t>2026-06-19 12:12:40</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-19 09:30:47</t>
+          <t>2026-06-19 12:12:43</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>E2E-3-1781842358</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>v3.0.0</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>紧急发布</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>回滚成功</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>问题3测试</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>e2e</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-06-19 12:12:38</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-06-19 12:12:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>E2E-DAEMON-1781837492</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>v8.8.8-daemon</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>常规发布</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>发布成功</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>E2E daemon测试</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>e2e_tester</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-06-19 10:51:32</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-06-19 10:51:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>E2E-EMERG-1781837489</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>v9.9.9-e2e</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>紧急发布</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>回滚成功</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>E2E紧急发布测试</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>e2e_tester</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-06-19 10:51:29</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-06-19 10:51:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>E2E-DAEMON-1781837351</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>v8.8.8-daemon</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>常规发布</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>已创建</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>E2E daemon测试</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>e2e_tester</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-06-19 10:49:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>E2E-EMERG-1781837349</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>v9.9.9-e2e</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>紧急发布</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>回滚失败</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>E2E紧急发布测试</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>e2e_tester</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-06-19 10:49:09</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-06-19 10:49:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>E2E-EMERG-1781837209</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>v9.9.9-e2e</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>紧急发布</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>回滚失败</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>E2E紧急发布测试</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>e2e_tester</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-06-19 10:46:49</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-06-19 10:46:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TEST-EMERG-002</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>v9.9.9-emerg</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>紧急发布</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>回滚成功</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>紧急发布测试</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>tester</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-06-19 10:28:49</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-06-19 10:30:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TEST-EMERG-001</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>v9.9.9-emerg</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>紧急发布</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>已创建</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>紧急发布测试</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>tester</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-06-19 10:26:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>REL-20260619_093038</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>v2.0619.38</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>常规发布</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>回滚失败</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>WMS 库存管理模块优化</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>developer01</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-06-19 09:30:38</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-06-19 09:30:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>REL-20260619_092918</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>v2.0619.50</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>常规发布</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>前置检查失败</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>WMS 库存管理模块优化</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>developer01</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>2026-06-19 09:29:18</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>2026-06-19 09:29:19</t>
         </is>
@@ -825,7 +1193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -847,21 +1215,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>前置检查失败</t>
+          <t>已创建</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>回滚失败</t>
+          <t>前置检查失败</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>发布成功</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>回滚失败</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>回滚成功</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -876,15 +1274,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
     <col width="23" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
   </cols>
@@ -934,38 +1332,318 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>E2E-4-1781842360</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>监控指标异常: 8 个仓库超标</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>524</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>ROLLBACK_SUCCESS</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-06-19 12:12:41</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-06-19 12:12:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>E2E-3-1781842358</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>监控指标异常: 8 个仓库超标</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>686</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ROLLBACK_SUCCESS</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-06-19 12:12:38</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-06-19 12:12:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>E2E-EMERG-1781837489</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>监控指标异常: 8 个仓库超标</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>v1.0.0-STABLE</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>554</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ROLLBACK_SUCCESS</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-06-19 10:51:29</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-06-19 10:51:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>E2E-EMERG-1781837349</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>监控指标异常: 8 个仓库超标</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>v1.0.0-STABLE</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>708</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ROLLBACK_FAILED</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-06-19 10:49:09</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-06-19 10:49:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>E2E-EMERG-1781837209</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>监控指标异常: 8 个仓库超标</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>v1.0.0-STABLE</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>423</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>ROLLBACK_FAILED</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-06-19 10:46:49</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-06-19 10:46:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TEST-EMERG-002</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>监控指标异常: 8 个仓库超标</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>635</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ROLLBACK_SUCCESS</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-06-19 10:30:16</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-06-19 10:30:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TEST-EMERG-002</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>监控指标异常: 1 个仓库超标</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>110</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ROLLBACK_SUCCESS</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-06-19 10:30:04</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-06-19 10:30:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>REL-20260619_093038</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>auto</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>监控指标异常</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>v2.05.12.stable</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E9" t="n">
         <v>727</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>ROLLBACK_FAILED</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>2026-06-19 09:30:44</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>2026-06-19 09:30:47</t>
         </is>

--- a/reports/weekly_report_20260615.xlsx
+++ b/reports/weekly_report_20260615.xlsx
@@ -519,7 +519,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.09</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="8">
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>36.36</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -675,10 +675,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -733,12 +733,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>E2E-4-1781842360</t>
+          <t>VERIFY-EMERG-1781843698</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>v4.0.0-OTHER</t>
+          <t>v7.7.7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -753,39 +753,39 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>问题4测试-其他版本</t>
+          <t>验证紧急发布</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>e2e</t>
+          <t>verify</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-19 12:12:40</t>
+          <t>2026-06-19 12:34:58</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-19 12:12:43</t>
+          <t>2026-06-19 12:35:01</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E2E-3-1781842358</t>
+          <t>QUICK-1781842469</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>v3.0.0</t>
+          <t>v1.0.0</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>紧急发布</t>
+          <t>常规发布</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -795,34 +795,34 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>问题3测试</t>
+          <t>快速测试</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>e2e</t>
+          <t>test</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-06-19 12:12:38</t>
+          <t>2026-06-19 12:14:29</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-06-19 12:12:40</t>
+          <t>2026-06-19 12:14:37</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E2E-DAEMON-1781837492</t>
+          <t>E2E-1-1781842365</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>v8.8.8-daemon</t>
+          <t>v1.0.0</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -832,39 +832,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>发布成功</t>
+          <t>回滚成功</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>E2E daemon测试</t>
+          <t>问题1测试</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>e2e_tester</t>
+          <t>e2e</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:51:32</t>
+          <t>2026-06-19 12:12:45</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:51:37</t>
+          <t>2026-06-19 12:12:52</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E2E-EMERG-1781837489</t>
+          <t>E2E-4-1781842360</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>v9.9.9-e2e</t>
+          <t>v4.0.0-OTHER</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -879,86 +879,91 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>E2E紧急发布测试</t>
+          <t>问题4测试-其他版本</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>e2e_tester</t>
+          <t>e2e</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-19 10:51:29</t>
+          <t>2026-06-19 12:12:40</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-06-19 10:51:32</t>
+          <t>2026-06-19 12:12:43</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E2E-DAEMON-1781837351</t>
+          <t>E2E-3-1781842358</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>v8.8.8-daemon</t>
+          <t>v3.0.0</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>常规发布</t>
+          <t>紧急发布</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>已创建</t>
+          <t>回滚成功</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>E2E daemon测试</t>
+          <t>问题3测试</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>e2e_tester</t>
+          <t>e2e</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-19 10:49:11</t>
+          <t>2026-06-19 12:12:38</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-06-19 12:12:40</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E2E-EMERG-1781837349</t>
+          <t>E2E-DAEMON-1781837492</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>v9.9.9-e2e</t>
+          <t>v8.8.8-daemon</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>紧急发布</t>
+          <t>常规发布</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>回滚失败</t>
+          <t>发布成功</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>E2E紧急发布测试</t>
+          <t>E2E daemon测试</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -968,19 +973,19 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-19 10:49:09</t>
+          <t>2026-06-19 10:51:32</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-06-19 10:49:11</t>
+          <t>2026-06-19 10:51:37</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E2E-EMERG-1781837209</t>
+          <t>E2E-EMERG-1781837489</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -995,7 +1000,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>回滚失败</t>
+          <t>回滚成功</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1010,66 +1015,61 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-06-19 10:46:49</t>
+          <t>2026-06-19 10:51:29</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-06-19 10:46:51</t>
+          <t>2026-06-19 10:51:32</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TEST-EMERG-002</t>
+          <t>E2E-DAEMON-1781837351</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>v9.9.9-emerg</t>
+          <t>v8.8.8-daemon</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>紧急发布</t>
+          <t>常规发布</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>回滚成功</t>
+          <t>已创建</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>紧急发布测试</t>
+          <t>E2E daemon测试</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>tester</t>
+          <t>e2e_tester</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-06-19 10:28:49</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>2026-06-19 10:30:16</t>
+          <t>2026-06-19 10:49:11</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TEST-EMERG-001</t>
+          <t>E2E-EMERG-1781837349</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>v9.9.9-emerg</t>
+          <t>v9.9.9-e2e</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1079,39 +1079,44 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>已创建</t>
+          <t>回滚失败</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>紧急发布测试</t>
+          <t>E2E紧急发布测试</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>tester</t>
+          <t>e2e_tester</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-06-19 10:26:56</t>
+          <t>2026-06-19 10:49:09</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026-06-19 10:49:11</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>REL-20260619_093038</t>
+          <t>E2E-EMERG-1781837209</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>v2.0619.38</t>
+          <t>v9.9.9-e2e</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>常规发布</t>
+          <t>紧急发布</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1121,62 +1126,183 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>WMS 库存管理模块优化</t>
+          <t>E2E紧急发布测试</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>developer01</t>
+          <t>e2e_tester</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-06-19 09:30:38</t>
+          <t>2026-06-19 10:46:49</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-06-19 09:30:47</t>
+          <t>2026-06-19 10:46:51</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>TEST-EMERG-002</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>v9.9.9-emerg</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>紧急发布</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>回滚成功</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>紧急发布测试</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>tester</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-06-19 10:28:49</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2026-06-19 10:30:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TEST-EMERG-001</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>v9.9.9-emerg</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>紧急发布</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>已创建</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>紧急发布测试</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>tester</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-06-19 10:26:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>REL-20260619_093038</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>v2.0619.38</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>常规发布</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>回滚失败</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>WMS 库存管理模块优化</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>developer01</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-06-19 09:30:38</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2026-06-19 09:30:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>REL-20260619_092918</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>v2.0619.50</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>常规发布</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>前置检查失败</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>WMS 库存管理模块优化</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>developer01</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>2026-06-19 09:29:18</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>2026-06-19 09:29:19</t>
         </is>
@@ -1259,7 +1385,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1274,10 +1400,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
@@ -1332,7 +1458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>E2E-4-1781842360</t>
+          <t>VERIFY-EMERG-1781843698</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1351,7 +1477,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>524</v>
+        <v>455</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1360,19 +1486,19 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-19 12:12:41</t>
+          <t>2026-06-19 12:34:59</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-19 12:12:43</t>
+          <t>2026-06-19 12:35:01</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E2E-3-1781842358</t>
+          <t>QUICK-1781842469</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1382,16 +1508,16 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>监控指标异常: 8 个仓库超标</t>
+          <t>监控指标异常: 1 个仓库超标</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>v1.0.0</t>
+          <t>v0.9.0</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>686</v>
+        <v>75</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1400,19 +1526,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-06-19 12:12:38</t>
+          <t>2026-06-19 12:14:35</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-06-19 12:12:40</t>
+          <t>2026-06-19 12:14:37</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E2E-EMERG-1781837489</t>
+          <t>E2E-1-1781842365</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1422,16 +1548,16 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>监控指标异常: 8 个仓库超标</t>
+          <t>监控指标异常: 1 个仓库超标</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>v1.0.0-STABLE</t>
+          <t>v0.9.0</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>554</v>
+        <v>113</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1440,19 +1566,19 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:51:29</t>
+          <t>2026-06-19 12:12:50</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:51:32</t>
+          <t>2026-06-19 12:12:52</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E2E-EMERG-1781837349</t>
+          <t>E2E-4-1781842360</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1467,32 +1593,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>v1.0.0-STABLE</t>
+          <t>v1.0.0</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>708</v>
+        <v>524</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ROLLBACK_FAILED</t>
+          <t>ROLLBACK_SUCCESS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-19 10:49:09</t>
+          <t>2026-06-19 12:12:41</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-06-19 10:49:11</t>
+          <t>2026-06-19 12:12:43</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E2E-EMERG-1781837209</t>
+          <t>E2E-3-1781842358</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1507,32 +1633,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>v1.0.0-STABLE</t>
+          <t>v1.0.0</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>423</v>
+        <v>686</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ROLLBACK_FAILED</t>
+          <t>ROLLBACK_SUCCESS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-19 10:46:49</t>
+          <t>2026-06-19 12:12:38</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-19 10:46:51</t>
+          <t>2026-06-19 12:12:40</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TEST-EMERG-002</t>
+          <t>E2E-EMERG-1781837489</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1547,11 +1673,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>v1.0.0</t>
+          <t>v1.0.0-STABLE</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>635</v>
+        <v>554</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1560,19 +1686,19 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-19 10:30:16</t>
+          <t>2026-06-19 10:51:29</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-06-19 10:30:16</t>
+          <t>2026-06-19 10:51:32</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TEST-EMERG-002</t>
+          <t>E2E-EMERG-1781837349</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1582,68 +1708,188 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>监控指标异常: 1 个仓库超标</t>
+          <t>监控指标异常: 8 个仓库超标</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>v1.0.0</t>
+          <t>v1.0.0-STABLE</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>110</v>
+        <v>708</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ROLLBACK_SUCCESS</t>
+          <t>ROLLBACK_FAILED</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-06-19 10:30:04</t>
+          <t>2026-06-19 10:49:09</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-06-19 10:30:04</t>
+          <t>2026-06-19 10:49:11</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>E2E-EMERG-1781837209</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>监控指标异常: 8 个仓库超标</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>v1.0.0-STABLE</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>423</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>ROLLBACK_FAILED</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-06-19 10:46:49</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-06-19 10:46:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TEST-EMERG-002</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>监控指标异常: 8 个仓库超标</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>635</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ROLLBACK_SUCCESS</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-06-19 10:30:16</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026-06-19 10:30:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TEST-EMERG-002</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>监控指标异常: 1 个仓库超标</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>110</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ROLLBACK_SUCCESS</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-06-19 10:30:04</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-06-19 10:30:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>REL-20260619_093038</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>auto</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>监控指标异常</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>v2.05.12.stable</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="E12" t="n">
         <v>727</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>ROLLBACK_FAILED</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>2026-06-19 09:30:44</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>2026-06-19 09:30:47</t>
         </is>

--- a/reports/weekly_report_20260615.xlsx
+++ b/reports/weekly_report_20260615.xlsx
@@ -12,6 +12,8 @@
     <sheet name="发布明细" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="状态分布" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="回滚记录" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="回滚复盘汇总" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="回滚复盘明细" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -519,7 +521,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -541,7 +543,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -561,7 +563,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -591,7 +593,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.14</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="8">
@@ -601,7 +603,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>50</v>
+        <v>56.25</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +623,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -661,7 +663,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -675,7 +677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -733,12 +735,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>VERIFY-EMERG-1781843698</t>
+          <t>FINAL-1781845306</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>v7.7.7</t>
+          <t>vFINAL-88</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -753,39 +755,39 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>验证紧急发布</t>
+          <t>最终验收-紧急发布</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>verify</t>
+          <t>qa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-19 12:34:58</t>
+          <t>2026-06-19 13:01:46</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-19 12:35:01</t>
+          <t>2026-06-19 13:01:48</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>QUICK-1781842469</t>
+          <t>FINAL-1781845285</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>v1.0.0</t>
+          <t>vFINAL-88</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>常规发布</t>
+          <t>紧急发布</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -795,39 +797,39 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>快速测试</t>
+          <t>最终验收-紧急发布</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>qa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-06-19 12:14:29</t>
+          <t>2026-06-19 13:01:25</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-06-19 12:14:37</t>
+          <t>2026-06-19 13:01:28</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E2E-1-1781842365</t>
+          <t>VERIFY-EMERG-1781843698</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>v1.0.0</t>
+          <t>v7.7.7</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>常规发布</t>
+          <t>紧急发布</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -837,39 +839,39 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>问题1测试</t>
+          <t>验证紧急发布</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>e2e</t>
+          <t>verify</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-19 12:12:45</t>
+          <t>2026-06-19 12:34:58</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-06-19 12:12:52</t>
+          <t>2026-06-19 12:35:01</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E2E-4-1781842360</t>
+          <t>QUICK-1781842469</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>v4.0.0-OTHER</t>
+          <t>v1.0.0</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>紧急发布</t>
+          <t>常规发布</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -879,39 +881,39 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>问题4测试-其他版本</t>
+          <t>快速测试</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>e2e</t>
+          <t>test</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:12:40</t>
+          <t>2026-06-19 12:14:29</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:12:43</t>
+          <t>2026-06-19 12:14:37</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E2E-3-1781842358</t>
+          <t>E2E-1-1781842365</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>v3.0.0</t>
+          <t>v1.0.0</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>紧急发布</t>
+          <t>常规发布</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -921,7 +923,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>问题3测试</t>
+          <t>问题1测试</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -931,66 +933,66 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-19 12:12:38</t>
+          <t>2026-06-19 12:12:45</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-19 12:12:40</t>
+          <t>2026-06-19 12:12:52</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E2E-DAEMON-1781837492</t>
+          <t>E2E-4-1781842360</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>v8.8.8-daemon</t>
+          <t>v4.0.0-OTHER</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>常规发布</t>
+          <t>紧急发布</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>发布成功</t>
+          <t>回滚成功</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>E2E daemon测试</t>
+          <t>问题4测试-其他版本</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>e2e_tester</t>
+          <t>e2e</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-19 10:51:32</t>
+          <t>2026-06-19 12:12:40</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-06-19 10:51:37</t>
+          <t>2026-06-19 12:12:43</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E2E-EMERG-1781837489</t>
+          <t>E2E-3-1781842358</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>v9.9.9-e2e</t>
+          <t>v3.0.0</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1005,29 +1007,29 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>E2E紧急发布测试</t>
+          <t>问题3测试</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>e2e_tester</t>
+          <t>e2e</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-06-19 10:51:29</t>
+          <t>2026-06-19 12:12:38</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-06-19 10:51:32</t>
+          <t>2026-06-19 12:12:40</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E2E-DAEMON-1781837351</t>
+          <t>E2E-DAEMON-1781837492</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1042,7 +1044,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>已创建</t>
+          <t>发布成功</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1057,14 +1059,19 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-06-19 10:49:11</t>
+          <t>2026-06-19 10:51:32</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-06-19 10:51:37</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E2E-EMERG-1781837349</t>
+          <t>E2E-EMERG-1781837489</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1079,7 +1086,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>回滚失败</t>
+          <t>回滚成功</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1094,39 +1101,39 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-06-19 10:49:09</t>
+          <t>2026-06-19 10:51:29</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-06-19 10:49:11</t>
+          <t>2026-06-19 10:51:32</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E2E-EMERG-1781837209</t>
+          <t>E2E-DAEMON-1781837351</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>v9.9.9-e2e</t>
+          <t>v8.8.8-daemon</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>紧急发布</t>
+          <t>常规发布</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>回滚失败</t>
+          <t>已创建</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>E2E紧急发布测试</t>
+          <t>E2E daemon测试</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1136,24 +1143,19 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-06-19 10:46:49</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2026-06-19 10:46:51</t>
+          <t>2026-06-19 10:49:11</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TEST-EMERG-002</t>
+          <t>E2E-EMERG-1781837349</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>v9.9.9-emerg</t>
+          <t>v9.9.9-e2e</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1163,39 +1165,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>回滚成功</t>
+          <t>回滚失败</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>紧急发布测试</t>
+          <t>E2E紧急发布测试</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>tester</t>
+          <t>e2e_tester</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-06-19 10:28:49</t>
+          <t>2026-06-19 10:49:09</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-06-19 10:30:16</t>
+          <t>2026-06-19 10:49:11</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TEST-EMERG-001</t>
+          <t>E2E-EMERG-1781837209</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>v9.9.9-emerg</t>
+          <t>v9.9.9-e2e</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1205,104 +1207,188 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>已创建</t>
+          <t>回滚失败</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>紧急发布测试</t>
+          <t>E2E紧急发布测试</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>tester</t>
+          <t>e2e_tester</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-06-19 10:26:56</t>
+          <t>2026-06-19 10:46:49</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-06-19 10:46:51</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>REL-20260619_093038</t>
+          <t>TEST-EMERG-002</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>v2.0619.38</t>
+          <t>v9.9.9-emerg</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>常规发布</t>
+          <t>紧急发布</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>回滚失败</t>
+          <t>回滚成功</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>WMS 库存管理模块优化</t>
+          <t>紧急发布测试</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>developer01</t>
+          <t>tester</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-06-19 09:30:38</t>
+          <t>2026-06-19 10:28:49</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-06-19 09:30:47</t>
+          <t>2026-06-19 10:30:16</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>TEST-EMERG-001</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>v9.9.9-emerg</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>紧急发布</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>已创建</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>紧急发布测试</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>tester</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-06-19 10:26:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>REL-20260619_093038</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>v2.0619.38</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>常规发布</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>回滚失败</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>WMS 库存管理模块优化</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>developer01</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-06-19 09:30:38</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-06-19 09:30:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>REL-20260619_092918</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>v2.0619.50</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>常规发布</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>前置检查失败</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>WMS 库存管理模块优化</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>developer01</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>2026-06-19 09:29:18</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>2026-06-19 09:29:19</t>
         </is>
@@ -1385,7 +1471,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1400,7 +1486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -1458,7 +1544,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>VERIFY-EMERG-1781843698</t>
+          <t>FINAL-1781845306</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1473,11 +1559,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>v1.0.0</t>
+          <t>vSTABLE-1</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>455</v>
+        <v>679</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1486,19 +1572,19 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-19 12:34:59</t>
+          <t>2026-06-19 13:01:46</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-19 12:35:01</t>
+          <t>2026-06-19 13:01:48</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>QUICK-1781842469</t>
+          <t>FINAL-1781845285</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1508,16 +1594,16 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>监控指标异常: 1 个仓库超标</t>
+          <t>监控指标异常: 8 个仓库超标</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>v0.9.0</t>
+          <t>vSTABLE-1</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>75</v>
+        <v>546</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1526,19 +1612,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-06-19 12:14:35</t>
+          <t>2026-06-19 13:01:25</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-06-19 12:14:37</t>
+          <t>2026-06-19 13:01:28</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E2E-1-1781842365</t>
+          <t>VERIFY-EMERG-1781843698</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1548,16 +1634,16 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>监控指标异常: 1 个仓库超标</t>
+          <t>监控指标异常: 8 个仓库超标</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>v0.9.0</t>
+          <t>v1.0.0</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>113</v>
+        <v>455</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1566,19 +1652,19 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-19 12:12:50</t>
+          <t>2026-06-19 12:34:59</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-06-19 12:12:52</t>
+          <t>2026-06-19 12:35:01</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E2E-4-1781842360</t>
+          <t>QUICK-1781842469</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1588,16 +1674,16 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>监控指标异常: 8 个仓库超标</t>
+          <t>监控指标异常: 1 个仓库超标</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>v1.0.0</t>
+          <t>v0.9.0</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>524</v>
+        <v>75</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1606,19 +1692,19 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:12:41</t>
+          <t>2026-06-19 12:14:35</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:12:43</t>
+          <t>2026-06-19 12:14:37</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E2E-3-1781842358</t>
+          <t>E2E-1-1781842365</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1628,16 +1714,16 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>监控指标异常: 8 个仓库超标</t>
+          <t>监控指标异常: 1 个仓库超标</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>v1.0.0</t>
+          <t>v0.9.0</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>686</v>
+        <v>113</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1646,19 +1732,19 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-19 12:12:38</t>
+          <t>2026-06-19 12:12:50</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-19 12:12:40</t>
+          <t>2026-06-19 12:12:52</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E2E-EMERG-1781837489</t>
+          <t>E2E-4-1781842360</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1673,11 +1759,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>v1.0.0-STABLE</t>
+          <t>v1.0.0</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>554</v>
+        <v>524</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1686,19 +1772,19 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-19 10:51:29</t>
+          <t>2026-06-19 12:12:41</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-06-19 10:51:32</t>
+          <t>2026-06-19 12:12:43</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E2E-EMERG-1781837349</t>
+          <t>E2E-3-1781842358</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1713,32 +1799,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>v1.0.0-STABLE</t>
+          <t>v1.0.0</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>708</v>
+        <v>686</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ROLLBACK_FAILED</t>
+          <t>ROLLBACK_SUCCESS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-06-19 10:49:09</t>
+          <t>2026-06-19 12:12:38</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-06-19 10:49:11</t>
+          <t>2026-06-19 12:12:40</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E2E-EMERG-1781837209</t>
+          <t>E2E-EMERG-1781837489</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1757,28 +1843,28 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>423</v>
+        <v>554</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ROLLBACK_FAILED</t>
+          <t>ROLLBACK_SUCCESS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-06-19 10:46:49</t>
+          <t>2026-06-19 10:51:29</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-06-19 10:46:51</t>
+          <t>2026-06-19 10:51:32</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TEST-EMERG-002</t>
+          <t>E2E-EMERG-1781837349</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1793,32 +1879,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>v1.0.0</t>
+          <t>v1.0.0-STABLE</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>635</v>
+        <v>708</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ROLLBACK_SUCCESS</t>
+          <t>ROLLBACK_FAILED</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-06-19 10:30:16</t>
+          <t>2026-06-19 10:49:09</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-06-19 10:30:16</t>
+          <t>2026-06-19 10:49:11</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TEST-EMERG-002</t>
+          <t>E2E-EMERG-1781837209</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1828,70 +1914,1054 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>监控指标异常: 1 个仓库超标</t>
+          <t>监控指标异常: 8 个仓库超标</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>v1.0.0</t>
+          <t>v1.0.0-STABLE</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>110</v>
+        <v>423</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ROLLBACK_SUCCESS</t>
+          <t>ROLLBACK_FAILED</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-06-19 10:30:04</t>
+          <t>2026-06-19 10:46:49</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-06-19 10:30:04</t>
+          <t>2026-06-19 10:46:51</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>TEST-EMERG-002</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>监控指标异常: 8 个仓库超标</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>635</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ROLLBACK_SUCCESS</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-06-19 10:30:16</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2026-06-19 10:30:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TEST-EMERG-002</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>监控指标异常: 1 个仓库超标</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>110</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ROLLBACK_SUCCESS</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-06-19 10:30:04</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-06-19 10:30:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>REL-20260619_093038</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>监控指标异常</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>v2.05.12.stable</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>727</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ROLLBACK_FAILED</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-06-19 09:30:44</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2026-06-19 09:30:47</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>指标</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>回滚总数</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>成功数</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>失败数</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>回滚成功率(%)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>76.92</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>自动回滚数</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>手动回滚数</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>总影响仓库数</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>总影响订单数</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>6235</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>需人工介入</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>发布单号</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>版本</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>触发类型</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>影响仓库数</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>影响仓库名称</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>影响订单</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>复查结果</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>需人工介入</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>复查异常仓库数</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>复查仓库总数</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>报告路径</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>FINAL-1781845306</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>vFINAL-88</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ROLLBACK_SUCCESS</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>华东中心仓, 华南中心仓, 华北中心仓, 西南区域仓, 华中区域仓, 东北区域仓, 西北区域仓, 海外保税仓</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>679</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>abnormal_needs_manual</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" t="n">
+        <v>8</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>E:\work\d012\reports\rollback_report_FINAL-1781845306_20260619_130146.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FINAL-1781845285</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>vFINAL-88</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ROLLBACK_SUCCESS</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>华东中心仓, 华南中心仓, 华北中心仓, 西南区域仓, 华中区域仓, 东北区域仓, 西北区域仓, 海外保税仓</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>546</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>abnormal_needs_manual</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>E:\work\d012\reports\rollback_report_FINAL-1781845285_20260619_130125.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>VERIFY-EMERG-1781843698</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>v7.7.7</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ROLLBACK_SUCCESS</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>华东中心仓, 华南中心仓, 华北中心仓, 西南区域仓, 华中区域仓, 东北区域仓, 西北区域仓, 海外保税仓</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>455</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>E:\work\d012\reports\rollback_report_VERIFY-EMERG-1781843698_20260619_123459.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>QUICK-1781842469</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ROLLBACK_SUCCESS</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>华东中心仓, 华南中心仓, 华北中心仓, 西南区域仓, 华中区域仓, 东北区域仓, 西北区域仓, 海外保税仓</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>75</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>E:\work\d012\reports\rollback_report_QUICK-1781842469_20260619_121435.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>E2E-1-1781842365</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ROLLBACK_SUCCESS</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>华东中心仓, 华南中心仓, 华北中心仓, 西南区域仓, 华中区域仓, 东北区域仓, 西北区域仓, 海外保税仓</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>113</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>E:\work\d012\reports\rollback_report_E2E-1-1781842365_20260619_121250.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>E2E-4-1781842360</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>v4.0.0-OTHER</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ROLLBACK_SUCCESS</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>8</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>华东中心仓, 华南中心仓, 华北中心仓, 西南区域仓, 华中区域仓, 东北区域仓, 西北区域仓, 海外保税仓</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>524</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>E:\work\d012\reports\rollback_report_E2E-4-1781842360_20260619_121241.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>E2E-3-1781842358</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>v3.0.0</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ROLLBACK_SUCCESS</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>华东中心仓, 华南中心仓, 华北中心仓, 西南区域仓, 华中区域仓, 东北区域仓, 西北区域仓, 海外保税仓</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>686</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>E:\work\d012\reports\rollback_report_E2E-3-1781842358_20260619_121238.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>E2E-EMERG-1781837489</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>v9.9.9-e2e</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ROLLBACK_SUCCESS</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>8</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>华东中心仓, 华南中心仓, 华北中心仓, 西南区域仓, 华中区域仓, 东北区域仓, 西北区域仓, 海外保税仓</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>554</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>E:\work\d012\reports\rollback_report_E2E-EMERG-1781837489_20260619_105129.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>E2E-EMERG-1781837349</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>v9.9.9-e2e</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ROLLBACK_FAILED</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>华东中心仓, 华南中心仓, 华北中心仓, 西南区域仓, 华中区域仓, 东北区域仓, 西北区域仓, 海外保税仓</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>708</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>E:\work\d012\reports\rollback_report_E2E-EMERG-1781837349_20260619_104909.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>E2E-EMERG-1781837209</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>v9.9.9-e2e</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ROLLBACK_FAILED</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>8</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>华东中心仓, 华南中心仓, 华北中心仓, 西南区域仓, 华中区域仓, 东北区域仓, 西北区域仓, 海外保税仓</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>423</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>E:\work\d012\reports\rollback_report_E2E-EMERG-1781837209_20260619_104649.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TEST-EMERG-002</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>v9.9.9-emerg</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>auto</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>监控指标异常</t>
-        </is>
-      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>v2.05.12.stable</t>
+          <t>ROLLBACK_SUCCESS</t>
         </is>
       </c>
       <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>635</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>E:\work\d012\reports\rollback_report_TEST-EMERG-002_20260619_103016.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TEST-EMERG-002</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>v9.9.9-emerg</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ROLLBACK_SUCCESS</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="n">
+        <v>110</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>E:\work\d012\reports\rollback_report_TEST-EMERG-002_20260619_103004.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>REL-20260619_093038</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>v2.0619.38</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ROLLBACK_FAILED</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>8</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>华东中心仓, 华南中心仓, 华北中心仓, 西南区域仓, 华中区域仓, 东北区域仓, 西北区域仓, 海外保税仓</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
         <v>727</v>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>ROLLBACK_FAILED</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>2026-06-19 09:30:44</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>2026-06-19 09:30:47</t>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>E:\work\d012\reports\rollback_report_REL-20260619_093038_20260619_093044.json</t>
         </is>
       </c>
     </row>
